--- a/MU/Test upload format/Normal/2028 - 2029/CP1 28-29.xlsx
+++ b/MU/Test upload format/Normal/2028 - 2029/CP1 28-29.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="34">
   <si>
     <t>custid</t>
   </si>
@@ -89,43 +89,49 @@
     <t>modifiedloancat</t>
   </si>
   <si>
-    <t>IA07</t>
-  </si>
-  <si>
-    <t>2829IA07</t>
+    <t>HomeStay</t>
+  </si>
+  <si>
+    <t>2728CR702</t>
+  </si>
+  <si>
+    <t>2829Q101</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>01-04-2029</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>01-04-2028</t>
+  </si>
+  <si>
+    <t>900000</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>01-04-2028</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>01-04-2029</t>
+    <t>K</t>
+  </si>
+  <si>
+    <t>2728CR703</t>
+  </si>
+  <si>
+    <t>2829Q102</t>
+  </si>
+  <si>
+    <t>1700000</t>
   </si>
   <si>
     <t>TP</t>
-  </si>
-  <si>
-    <t>IA19</t>
-  </si>
-  <si>
-    <t>2829IA19</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>IA17</t>
-  </si>
-  <si>
-    <t>2829IA17</t>
-  </si>
-  <si>
-    <t>S</t>
   </si>
 </sst>
 </file>
@@ -312,7 +318,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,13 +339,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.25"/>
+        <fgColor theme="5" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -690,7 +690,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -714,16 +714,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -732,89 +732,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -831,27 +831,22 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1173,8 +1168,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3"/>
+  <dimension ref="A1:T3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="17.8571428571429" customWidth="1"/>
     <col min="2" max="2" width="24.5714285714286" customWidth="1"/>
@@ -1192,7 +1187,7 @@
     <col min="15" max="15" width="13.2857142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1250,25 +1245,31 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:19">
+    <row r="2" s="1" customFormat="1" spans="1:20">
       <c r="A2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8">
-        <v>10000</v>
+      <c r="B2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="9">
-        <v>1000</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>23</v>
@@ -1285,11 +1286,11 @@
       <c r="L2" s="12">
         <v>1</v>
       </c>
-      <c r="M2" s="9">
-        <v>100000</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>22</v>
+      <c r="M2" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="O2" s="10"/>
       <c r="P2" s="1" t="s">
@@ -1299,51 +1300,57 @@
         <v>23</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="S2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="S2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:20">
+      <c r="A3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="9" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:19">
-      <c r="A3" s="13" t="s">
+      <c r="G3" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="13">
-        <v>1000</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="13">
-        <v>1000</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>22</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>24</v>
       </c>
       <c r="J3" s="2">
         <v>1</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="14">
         <v>0</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="15">
         <v>1</v>
       </c>
-      <c r="M3" s="13">
-        <v>100000</v>
-      </c>
-      <c r="N3" s="14" t="s">
-        <v>22</v>
+      <c r="M3" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="P3" s="2" t="s">
         <v>23</v>
@@ -1352,58 +1359,17 @@
         <v>23</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S3" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:19">
-      <c r="A4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="7">
-        <v>10000</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="13">
-        <v>1000</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="2">
-        <v>1</v>
-      </c>
-      <c r="K4" s="15">
-        <v>0</v>
-      </c>
-      <c r="L4" s="16">
-        <v>1</v>
-      </c>
-      <c r="M4" s="7">
-        <v>100000</v>
-      </c>
-      <c r="N4" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="S4" t="s">
-        <v>31</v>
+      <c r="S3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O1" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O3" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
